--- a/results/Int Task Remove ACC -0.8/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_8_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6124827675265162</v>
+        <v>0.6309619123072144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6133125438446476</v>
+        <v>0.596684733860807</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6116550852811118</v>
+        <v>0.5902904827884672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6116550852811118</v>
+        <v>0.6110546099266028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5998183391909201</v>
+        <v>0.6067128991389871</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6002134209121083</v>
+        <v>0.5893783396097346</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6028612013695236</v>
+        <v>0.5899308257975799</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5985591034576631</v>
+        <v>0.6081681051782928</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.598832205442495</v>
+        <v>0.5979387344122461</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5982797192546497</v>
+        <v>0.6019666833029111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5997005476000181</v>
+        <v>0.5806115041375387</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5883370619461614</v>
+        <v>0.5740535663803603</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5806397741193552</v>
+        <v>0.5740535663803603</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5691918275321701</v>
+        <v>0.5605029962690604</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.569507683501848</v>
+        <v>0.5712014393259878</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.570611608841175</v>
+        <v>0.5736813449531102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5433771459882801</v>
+        <v>0.5598639550751597</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.540220680364229</v>
+        <v>0.5674455453837912</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.532289903428346</v>
+        <v>0.5332341557222282</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5386820604279586</v>
+        <v>0.5331163641313263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5386820604279586</v>
+        <v>0.5357630975523779</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4964564799335481</v>
+        <v>0.5361175193614474</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4964564799335481</v>
+        <v>0.5658392170960098</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5288926194406731</v>
+        <v>0.5654441353748216</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5286163763467505</v>
+        <v>0.5626420915598398</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5418760448550378</v>
+        <v>0.5675478059353001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5485048320728179</v>
+        <v>0.5762322745468951</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5499652732939415</v>
+        <v>0.5190436718867246</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5320480380283608</v>
+        <v>0.526387584940825</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5229747699137591</v>
+        <v>0.5277688004104383</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5249887443590916</v>
+        <v>0.5314412804556703</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4947187485821383</v>
+        <v>0.5251939634863518</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4913235586671925</v>
+        <v>0.5193209620170108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4917175933520171</v>
+        <v>0.5295107199073024</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4917175933520171</v>
+        <v>0.5300214991466654</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4885965524582669</v>
+        <v>0.5093678343448869</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4842141817585325</v>
+        <v>0.5163573255899178</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4924306251156103</v>
+        <v>0.4854180990705808</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4588863721237039</v>
+        <v>0.497899121536491</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4493752683030682</v>
+        <v>0.5046394181269915</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4490594123333904</v>
+        <v>0.5115934846417216</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4430612900186023</v>
+        <v>0.4990759904091469</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4365482003189971</v>
+        <v>0.5184400554231249</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4241526858227786</v>
+        <v>0.5177697776443776</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4174415317443975</v>
+        <v>0.5081773539995045</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4139306443112769</v>
+        <v>0.4949072151275814</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3890165885461202</v>
+        <v>0.477469522516517</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3863271011402226</v>
+        <v>0.4821354655647191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3879470409007305</v>
+        <v>0.5014037267514301</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3896451593763852</v>
+        <v>0.5014037267514301</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3780387612861795</v>
+        <v>0.4883806884613102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3676477979080213</v>
+        <v>0.4716216499199017</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4323679076374323</v>
+        <v>0.4716216499199017</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4563082195844662</v>
+        <v>0.4785245861588773</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4650708669112078</v>
+        <v>0.4746519476621423</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4698399430412218</v>
+        <v>0.4800506416587848</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4714244580714289</v>
+        <v>0.4798140114406173</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4814421529859732</v>
+        <v>0.471996837950182</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.454498591736091</v>
+        <v>0.4715246245502106</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4440284026064225</v>
+        <v>0.4762666522408323</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4601661995721111</v>
+        <v>0.4763479720650698</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4618643180477658</v>
+        <v>0.4430256907822409</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4641524415142938</v>
+        <v>0.4472173263577444</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4641524415142938</v>
+        <v>0.4606396345145067</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4932008948670787</v>
+        <v>0.4389415509400642</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4212171448714414</v>
+        <v>0.4375603354704509</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4137659105900748</v>
+        <v>0.4318738809798864</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4165679544050565</v>
+        <v>0.4669473305807911</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4204707824502745</v>
+        <v>0.4657631324535901</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4621773819204741</v>
+        <v>0.4538794442330982</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4607513183932878</v>
+        <v>0.4196607253169903</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4617384991780764</v>
+        <v>0.4196607253169903</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4649762846263651</v>
+        <v>0.4225430419198459</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4708170024744959</v>
+        <v>0.4225430419198459</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4678690715928564</v>
+        <v>0.4575519242783302</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4799797921981831</v>
+        <v>0.4145112259748781</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4795513798194211</v>
+        <v>0.42448424733791</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4553878746208856</v>
+        <v>0.4096754885297166</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4490990252091455</v>
+        <v>0.4217979010411032</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4771414511225975</v>
+        <v>0.4339630675373356</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4805814890951163</v>
+        <v>0.4451888679093825</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4887958383794669</v>
+        <v>0.4458987585638849</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.477355221046827</v>
+        <v>0.4461343417456888</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4779420849286096</v>
+        <v>0.4673874348656128</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4701290995836285</v>
+        <v>0.4930363356519372</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4791711311133836</v>
+        <v>0.4930363356519372</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4797621831406205</v>
+        <v>0.4988384876606765</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4924412699853066</v>
+        <v>0.4798445500012216</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4976544640395361</v>
+        <v>0.4929332025701252</v>
       </c>
     </row>
   </sheetData>
